--- a/05_final_results/TableS_benchmark_precision_recall.xlsx
+++ b/05_final_results/TableS_benchmark_precision_recall.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,116 +429,116 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Gold Yes</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>FN</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>TN</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Specificity</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>All-Yes baseline acc.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>[Q4]: Pick-and-mix SSP/RCP</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L2" t="n">
         <v>0.6919999999999999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.846</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>[Q5]: Customised scenarios</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -538,10 +550,10 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0.923</v>
+        <v>0.962</v>
       </c>
       <c r="I3" t="n">
-        <v>0.909</v>
+        <v>0.958</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -550,121 +562,121 @@
         <v>0.667</v>
       </c>
       <c r="L3" t="n">
-        <v>0.769</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>[Q6]: Co-produced scenarios</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
         <v>4</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H4" t="n">
-        <v>0.769</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0.909</v>
       </c>
       <c r="J4" t="n">
-        <v>0.571</v>
+        <v>0.714</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0.917</v>
       </c>
       <c r="L4" t="n">
         <v>0.538</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>[Q7] Baseline scenario</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H5" t="n">
-        <v>0.846</v>
+        <v>0.769</v>
       </c>
       <c r="I5" t="n">
-        <v>0.75</v>
+        <v>0.444</v>
       </c>
       <c r="J5" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.889</v>
+        <v>0.762</v>
       </c>
       <c r="L5" t="n">
-        <v>0.308</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>[Q9]: Acute physical risk damage</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0.962</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0.962</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
@@ -672,22 +684,22 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>[Q11]: Scale of scenarios</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -696,35 +708,35 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0.962</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L7" t="n">
         <v>0.923</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>[Q13]: Justification for choice</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -748,47 +760,47 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.769</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>All binary questions</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>182</v>
       </c>
       <c r="C9" t="n">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>123</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="H9" t="n">
         <v>0.89</v>
       </c>
       <c r="I9" t="n">
-        <v>0.967</v>
+        <v>0.925</v>
       </c>
       <c r="J9" t="n">
-        <v>0.881</v>
+        <v>0.925</v>
       </c>
       <c r="K9" t="n">
-        <v>0.917</v>
+        <v>0.796</v>
       </c>
       <c r="L9" t="n">
-        <v>0.736</v>
+        <v>0.731</v>
       </c>
     </row>
   </sheetData>
